--- a/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -632,39 +632,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,96; -1,22</t>
+          <t>-26,53; -1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 28,97</t>
+          <t>0,82; 28,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 1,59</t>
+          <t>-28,49; -0,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-70,01; -4,7</t>
+          <t>-70,51; -5,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 109,98</t>
+          <t>2,19; 112,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 3,28</t>
+          <t>-57,21; -0,95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,39 +712,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 4,72</t>
+          <t>-13,19; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 12,64</t>
+          <t>-10,72; 11,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,63</t>
+          <t>-2,32; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,93; 23,59</t>
+          <t>-44,74; 24,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 39,38</t>
+          <t>-24,49; 34,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 769,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 14,28</t>
+          <t>-8,87; 13,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 11,0</t>
+          <t>-10,25; 11,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 14,39</t>
+          <t>-7,71; 14,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 102,24</t>
+          <t>-35,79; 96,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 92,41</t>
+          <t>-46,84; 95,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 129,12</t>
+          <t>-34,11; 138,41</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 7,88</t>
+          <t>-15,15; 9,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 17,59</t>
+          <t>-8,51; 16,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 7,26</t>
+          <t>-30,87; 6,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 29,97</t>
+          <t>-37,41; 34,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 87,39</t>
+          <t>-28,18; 83,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 17,68</t>
+          <t>-43,09; 15,76</t>
         </is>
       </c>
     </row>
@@ -952,27 +952,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 13,5</t>
+          <t>-16,31; 14,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 9,12</t>
+          <t>-10,76; 9,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 78,45</t>
+          <t>-54,72; 87,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 185,64</t>
+          <t>-75,22; 206,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1032,39 +1032,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 19,64</t>
+          <t>-5,58; 19,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 20,72</t>
+          <t>-9,29; 20,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -0,93</t>
+          <t>-24,68; -0,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 131,45</t>
+          <t>-24,0; 149,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 86,33</t>
+          <t>-26,29; 86,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,64; -2,26</t>
+          <t>-86,74; 9,73</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 7,01</t>
+          <t>-9,04; 7,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 7,54</t>
+          <t>-9,4; 8,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 4,81</t>
+          <t>-16,26; 5,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 37,79</t>
+          <t>-35,7; 39,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 32,63</t>
+          <t>-29,17; 34,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 21,54</t>
+          <t>-44,98; 21,64</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 1,71</t>
+          <t>-16,88; 0,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 12,11</t>
+          <t>-5,32; 11,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,17</t>
+          <t>-3,84; 4,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 3,48</t>
+          <t>-29,13; 1,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 42,26</t>
+          <t>-14,59; 40,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 222,57</t>
+          <t>-67,04; 213,94</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,53</t>
+          <t>-7,22; 0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,94</t>
+          <t>-0,53; 7,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,92</t>
+          <t>-9,54; -0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 1,52</t>
+          <t>-21,44; 1,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 25,45</t>
+          <t>-1,79; 27,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,39; -4,53</t>
+          <t>-40,27; -2,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,53; -1,6</t>
+          <t>-26,95; -1,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 28,19</t>
+          <t>0,37; 28,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -0,3</t>
+          <t>-28,38; -0,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-70,51; -5,77</t>
+          <t>-69,58; -6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 112,18</t>
+          <t>1,2; 109,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,21; -0,95</t>
+          <t>-58,66; -3,8</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 4,7</t>
+          <t>-13,41; 5,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 11,34</t>
+          <t>-9,01; 12,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,85</t>
+          <t>-2,24; 2,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 24,08</t>
+          <t>-45,91; 31,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 34,14</t>
+          <t>-20,99; 39,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 13,85</t>
+          <t>-8,75; 13,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 11,57</t>
+          <t>-10,68; 12,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 14,95</t>
+          <t>-7,31; 13,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 96,61</t>
+          <t>-35,9; 98,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 95,35</t>
+          <t>-48,52; 97,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 138,41</t>
+          <t>-32,37; 131,4</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 9,76</t>
+          <t>-15,82; 8,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 16,69</t>
+          <t>-7,27; 16,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 6,81</t>
+          <t>-33,4; 5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 34,09</t>
+          <t>-39,54; 29,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 83,26</t>
+          <t>-24,47; 83,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 15,76</t>
+          <t>-46,47; 13,66</t>
         </is>
       </c>
     </row>
@@ -952,27 +952,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 14,25</t>
+          <t>-17,11; 13,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 9,97</t>
+          <t>-12,1; 10,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 87,37</t>
+          <t>-52,92; 84,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,22; 206,32</t>
+          <t>-78,8; 256,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 19,89</t>
+          <t>-5,46; 19,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 20,3</t>
+          <t>-10,97; 20,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,68; -0,07</t>
+          <t>-25,68; -2,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 149,29</t>
+          <t>-23,52; 141,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 86,87</t>
+          <t>-28,64; 90,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,74; 9,73</t>
+          <t>-87,34; 2,74</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,48</t>
+          <t>-9,66; 6,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 8,13</t>
+          <t>-9,3; 8,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 5,22</t>
+          <t>-16,53; 4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 39,16</t>
+          <t>-36,69; 37,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 34,79</t>
+          <t>-28,44; 35,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 21,64</t>
+          <t>-44,75; 17,75</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 0,96</t>
+          <t>-16,26; 0,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 11,25</t>
+          <t>-4,56; 11,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,04</t>
+          <t>-3,57; 3,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 1,89</t>
+          <t>-27,96; 1,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 40,89</t>
+          <t>-12,44; 40,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 213,94</t>
+          <t>-62,48; 201,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,51</t>
+          <t>-7,34; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,31</t>
+          <t>-0,98; 6,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,54</t>
+          <t>-9,07; 0,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 1,72</t>
+          <t>-21,84; 3,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 27,57</t>
+          <t>-3,48; 25,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,27; -2,88</t>
+          <t>-38,81; 0,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Provincia-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-13,97</t>
+          <t>-10,49</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-33,51%</t>
+          <t>-23,84%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,95; -1,88</t>
+          <t>-26,96; -1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 28,46</t>
+          <t>-0,14; 28,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,38; -0,85</t>
+          <t>-25,01; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,58; -6,27</t>
+          <t>-70,01; -4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 109,73</t>
+          <t>-0,85; 109,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -3,8</t>
+          <t>-48,21; 11,89</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,46%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 5,82</t>
+          <t>-14,28; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 12,97</t>
+          <t>-9,33; 12,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,56</t>
+          <t>-1,5; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 31,84</t>
+          <t>-47,93; 23,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 39,18</t>
+          <t>-21,37; 39,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 13,37</t>
+          <t>-9,06; 14,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 12,11</t>
+          <t>-10,44; 11,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 13,91</t>
+          <t>-8,25; 13,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 98,37</t>
+          <t>-35,78; 102,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 97,38</t>
+          <t>-46,95; 92,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 131,4</t>
+          <t>-37,57; 116,23</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-10,9</t>
+          <t>-8,86</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,65%</t>
+          <t>-15,26%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 8,27</t>
+          <t>-17,61; 7,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 16,15</t>
+          <t>-7,21; 17,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 5,89</t>
+          <t>-30,89; 9,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 29,3</t>
+          <t>-39,85; 29,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 83,07</t>
+          <t>-23,08; 87,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 13,66</t>
+          <t>-42,51; 22,95</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -952,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 13,99</t>
+          <t>-17,13; 13,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 10,76</t>
+          <t>-12,74; 9,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 84,95</t>
+          <t>-54,39; 78,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-78,8; 256,37</t>
+          <t>-80,09; 185,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,75</t>
+          <t>-12,48</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-59,2%</t>
+          <t>-58,58%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 19,44</t>
+          <t>-5,96; 19,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 20,77</t>
+          <t>-9,42; 20,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,68; -2,14</t>
+          <t>-25,12; -1,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 141,94</t>
+          <t>-26,42; 131,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 90,16</t>
+          <t>-25,7; 86,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,34; 2,74</t>
+          <t>-87,55; 0,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,96%</t>
+          <t>-23,33%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 6,82</t>
+          <t>-9,54; 7,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 8,18</t>
+          <t>-9,52; 7,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 4,28</t>
+          <t>-18,01; 2,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 37,04</t>
+          <t>-37,19; 37,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 35,54</t>
+          <t>-29,5; 32,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 17,75</t>
+          <t>-46,25; 12,14</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1179,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 0,89</t>
+          <t>-16,62; 1,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 11,13</t>
+          <t>-5,56; 12,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,91</t>
+          <t>-3,36; 3,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 1,8</t>
+          <t>-28,71; 3,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 40,06</t>
+          <t>-15,69; 42,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,48; 201,59</t>
+          <t>-64,98; 232,61</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1259,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-21,44%</t>
+          <t>-17,41%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,97</t>
+          <t>-7,06; 0,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,79</t>
+          <t>-1,04; 6,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,12</t>
+          <t>-8,0; 0,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 3,23</t>
+          <t>-21,49; 1,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 25,5</t>
+          <t>-3,73; 25,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 0,71</t>
+          <t>-34,2; 1,44</t>
         </is>
       </c>
     </row>
